--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -499,19 +499,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>11068.54145946911</v>
+        <v>14142.24936708983</v>
       </c>
       <c r="G2" t="n">
-        <v>26598.303</v>
+        <v>71653.867</v>
       </c>
       <c r="H2" t="n">
-        <v>-26598.303</v>
+        <v>-71653.867</v>
       </c>
       <c r="I2" t="n">
-        <v>7773449.460466523</v>
+        <v>18411142.67508465</v>
       </c>
       <c r="J2" t="n">
-        <v>7493362.390892057</v>
+        <v>18119791.7504724</v>
       </c>
     </row>
     <row r="3">
@@ -524,16 +524,16 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>5994179.6</v>
+        <v>3764198.8</v>
       </c>
       <c r="D3" t="n">
-        <v>5994179.6</v>
+        <v>3764198.8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-7.0938653e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>997039.6439429374</v>
+        <v>382677.3822792529</v>
       </c>
       <c r="G3" t="n">
         <v>34830</v>
@@ -542,10 +542,10 @@
         <v>-34830</v>
       </c>
       <c r="I3" t="n">
-        <v>17115424.80015815</v>
+        <v>14169672.93929925</v>
       </c>
       <c r="J3" t="n">
-        <v>16226961.8072235</v>
+        <v>13609148.28703685</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speicher_Statistiken" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Speicher_Statistiken" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,19 +499,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>11068.54145946911</v>
+        <v>9614.717851404772</v>
       </c>
       <c r="G2" t="n">
-        <v>26598.303</v>
+        <v>68054.62</v>
       </c>
       <c r="H2" t="n">
-        <v>-26598.303</v>
+        <v>-68054.62</v>
       </c>
       <c r="I2" t="n">
-        <v>7773449.460466523</v>
+        <v>13081695.89776278</v>
       </c>
       <c r="J2" t="n">
-        <v>7493362.390892057</v>
+        <v>12791244.7838653</v>
       </c>
     </row>
     <row r="3">
@@ -524,16 +524,16 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>5994179.6</v>
+        <v>4161446.1</v>
       </c>
       <c r="D3" t="n">
-        <v>5994179.6</v>
+        <v>4161446.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-5.3829591e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>997039.6439429374</v>
+        <v>304728.4216042956</v>
       </c>
       <c r="G3" t="n">
         <v>34830</v>
@@ -542,10 +542,44 @@
         <v>-34830</v>
       </c>
       <c r="I3" t="n">
-        <v>17115424.80015815</v>
+        <v>13553761.4851619</v>
       </c>
       <c r="J3" t="n">
-        <v>16226961.8072235</v>
+        <v>12934818.12017475</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wasserstoffkaverne_H2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8759</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3649659.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3649659.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>444769.5968098919</v>
+      </c>
+      <c r="G4" t="n">
+        <v>47000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-47000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20219662.573226</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19068569.02585775</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -499,19 +499,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9614.717851404772</v>
+        <v>15755.74439211646</v>
       </c>
       <c r="G2" t="n">
-        <v>68054.62</v>
+        <v>45852.825</v>
       </c>
       <c r="H2" t="n">
-        <v>-68054.62</v>
+        <v>-45852.825</v>
       </c>
       <c r="I2" t="n">
-        <v>13081695.89776278</v>
+        <v>32944368.41072987</v>
       </c>
       <c r="J2" t="n">
-        <v>12791244.7838653</v>
+        <v>32932905.22630939</v>
       </c>
     </row>
     <row r="3">
@@ -524,16 +524,16 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>4161446.1</v>
+        <v>2650628.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4161446.1</v>
+        <v>2650628.4</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.3829591e-12</v>
+        <v>-3.8743032e-11</v>
       </c>
       <c r="F3" t="n">
-        <v>304728.4216042956</v>
+        <v>216799.2042384782</v>
       </c>
       <c r="G3" t="n">
         <v>34830</v>
@@ -542,10 +542,10 @@
         <v>-34830</v>
       </c>
       <c r="I3" t="n">
-        <v>13553761.4851619</v>
+        <v>13446677.078684</v>
       </c>
       <c r="J3" t="n">
-        <v>12934818.12017475</v>
+        <v>13439833.26640703</v>
       </c>
     </row>
     <row r="4">
@@ -558,28 +558,28 @@
         <v>8759</v>
       </c>
       <c r="C4" t="n">
-        <v>3649659.4</v>
+        <v>40051246</v>
       </c>
       <c r="D4" t="n">
-        <v>3649659.4</v>
+        <v>27328292</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>444769.5968098919</v>
+        <v>13228554.86678605</v>
       </c>
       <c r="G4" t="n">
-        <v>47000</v>
+        <v>131144.08</v>
       </c>
       <c r="H4" t="n">
-        <v>-47000</v>
+        <v>-131144.08</v>
       </c>
       <c r="I4" t="n">
-        <v>20219662.573226</v>
+        <v>85058362.53500324</v>
       </c>
       <c r="J4" t="n">
-        <v>19068569.02585775</v>
+        <v>85074755.40955251</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -490,28 +490,28 @@
         <v>35036</v>
       </c>
       <c r="C2" t="n">
-        <v>525000</v>
+        <v>149031.61</v>
       </c>
       <c r="D2" t="n">
-        <v>525000</v>
+        <v>149031.61</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15755.74439211646</v>
+        <v>5128.406679758545</v>
       </c>
       <c r="G2" t="n">
-        <v>45852.825</v>
+        <v>74515.807</v>
       </c>
       <c r="H2" t="n">
-        <v>-45852.825</v>
+        <v>-74515.807</v>
       </c>
       <c r="I2" t="n">
-        <v>32944368.41072987</v>
+        <v>27265211.72264488</v>
       </c>
       <c r="J2" t="n">
-        <v>32932905.22630939</v>
+        <v>27246582.78093103</v>
       </c>
     </row>
     <row r="3">
@@ -524,28 +524,28 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>2650628.4</v>
+        <v>62140</v>
       </c>
       <c r="D3" t="n">
-        <v>2650628.4</v>
+        <v>62140</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.8743032e-11</v>
+        <v>-9.4190381e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>216799.2042384782</v>
+        <v>14515.42882472999</v>
       </c>
       <c r="G3" t="n">
-        <v>34830</v>
+        <v>6214</v>
       </c>
       <c r="H3" t="n">
-        <v>-34830</v>
+        <v>-6214</v>
       </c>
       <c r="I3" t="n">
-        <v>13446677.078684</v>
+        <v>4696381.3248575</v>
       </c>
       <c r="J3" t="n">
-        <v>13439833.26640703</v>
+        <v>4696070.6249155</v>
       </c>
     </row>
     <row r="4">
@@ -558,28 +558,28 @@
         <v>8759</v>
       </c>
       <c r="C4" t="n">
-        <v>40051246</v>
+        <v>41324434</v>
       </c>
       <c r="D4" t="n">
-        <v>27328292</v>
+        <v>27801942</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>13228554.86678605</v>
+        <v>13306055.14941759</v>
       </c>
       <c r="G4" t="n">
-        <v>131144.08</v>
+        <v>173349.98</v>
       </c>
       <c r="H4" t="n">
-        <v>-131144.08</v>
+        <v>-173349.98</v>
       </c>
       <c r="I4" t="n">
-        <v>85058362.53500324</v>
+        <v>86828387.579575</v>
       </c>
       <c r="J4" t="n">
-        <v>85074755.40955251</v>
+        <v>86831082.15900075</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -499,7 +499,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>14142.24936708983</v>
+        <v>14482.08508911288</v>
       </c>
       <c r="G2" t="n">
         <v>71653.867</v>
@@ -508,10 +508,10 @@
         <v>-71653.867</v>
       </c>
       <c r="I2" t="n">
-        <v>18411142.67508465</v>
+        <v>19239612.40794263</v>
       </c>
       <c r="J2" t="n">
-        <v>18119791.7504724</v>
+        <v>18948261.48692221</v>
       </c>
     </row>
     <row r="3">
@@ -524,16 +524,16 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>3764198.8</v>
+        <v>3588449.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3764198.8</v>
+        <v>3588449.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.0938653e-12</v>
+        <v>-1.3805432e-11</v>
       </c>
       <c r="F3" t="n">
-        <v>382677.3822792529</v>
+        <v>313275.22446899</v>
       </c>
       <c r="G3" t="n">
         <v>34830</v>
@@ -542,10 +542,10 @@
         <v>-34830</v>
       </c>
       <c r="I3" t="n">
-        <v>14169672.93929925</v>
+        <v>13557936.64661725</v>
       </c>
       <c r="J3" t="n">
-        <v>13609148.28703685</v>
+        <v>13023257.45264375</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -490,28 +490,28 @@
         <v>35036</v>
       </c>
       <c r="C2" t="n">
-        <v>149031.61</v>
+        <v>13056.451</v>
       </c>
       <c r="D2" t="n">
-        <v>149031.61</v>
+        <v>13056.451</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5128.406679758545</v>
+        <v>564.4819898670934</v>
       </c>
       <c r="G2" t="n">
-        <v>74515.807</v>
+        <v>6528.2254</v>
       </c>
       <c r="H2" t="n">
-        <v>-74515.807</v>
+        <v>-6528.2254</v>
       </c>
       <c r="I2" t="n">
-        <v>27265211.72264488</v>
+        <v>5743156.733424547</v>
       </c>
       <c r="J2" t="n">
-        <v>27246582.78093103</v>
+        <v>5741524.676851236</v>
       </c>
     </row>
     <row r="3">
@@ -524,28 +524,28 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>62140</v>
+        <v>82335.378</v>
       </c>
       <c r="D3" t="n">
-        <v>62140</v>
+        <v>82335.378</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.4190381e-12</v>
+        <v>-9.378499e-12</v>
       </c>
       <c r="F3" t="n">
-        <v>14515.42882472999</v>
+        <v>15181.55290432287</v>
       </c>
       <c r="G3" t="n">
-        <v>6214</v>
+        <v>8233.5378</v>
       </c>
       <c r="H3" t="n">
-        <v>-6214</v>
+        <v>-8233.5378</v>
       </c>
       <c r="I3" t="n">
-        <v>4696381.3248575</v>
+        <v>5336761.97755825</v>
       </c>
       <c r="J3" t="n">
-        <v>4696070.6249155</v>
+        <v>5336350.295019325</v>
       </c>
     </row>
     <row r="4">
@@ -558,28 +558,28 @@
         <v>8759</v>
       </c>
       <c r="C4" t="n">
-        <v>41324434</v>
+        <v>11980062</v>
       </c>
       <c r="D4" t="n">
-        <v>27801942</v>
+        <v>9455792.300000001</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>13306055.14941759</v>
+        <v>3816302.330308144</v>
       </c>
       <c r="G4" t="n">
-        <v>173349.98</v>
+        <v>54135.627</v>
       </c>
       <c r="H4" t="n">
-        <v>-173349.98</v>
+        <v>-54135.627</v>
       </c>
       <c r="I4" t="n">
-        <v>86828387.579575</v>
+        <v>25522073.3914841</v>
       </c>
       <c r="J4" t="n">
-        <v>86831082.15900075</v>
+        <v>25531009.81323275</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Speicher_Statistiken" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speicher_Statistiken" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,28 +490,28 @@
         <v>35036</v>
       </c>
       <c r="C2" t="n">
-        <v>149031.61</v>
+        <v>45170.431</v>
       </c>
       <c r="D2" t="n">
-        <v>149031.61</v>
+        <v>45170.431</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-3.3107066e-14</v>
       </c>
       <c r="F2" t="n">
-        <v>5128.406679758545</v>
+        <v>2465.805483493737</v>
       </c>
       <c r="G2" t="n">
-        <v>74515.807</v>
+        <v>22585.215</v>
       </c>
       <c r="H2" t="n">
-        <v>-74515.807</v>
+        <v>-22585.215</v>
       </c>
       <c r="I2" t="n">
-        <v>27265211.72264488</v>
+        <v>21497116.57352501</v>
       </c>
       <c r="J2" t="n">
-        <v>27246582.78093103</v>
+        <v>21491470.26829587</v>
       </c>
     </row>
     <row r="3">
@@ -524,28 +524,28 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>62140</v>
+        <v>266521.3</v>
       </c>
       <c r="D3" t="n">
-        <v>62140</v>
+        <v>266521.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.4190381e-12</v>
+        <v>-3.1580267e-11</v>
       </c>
       <c r="F3" t="n">
-        <v>14515.42882472999</v>
+        <v>59587.17277239982</v>
       </c>
       <c r="G3" t="n">
-        <v>6214</v>
+        <v>26652.13</v>
       </c>
       <c r="H3" t="n">
-        <v>-6214</v>
+        <v>-26652.13</v>
       </c>
       <c r="I3" t="n">
-        <v>4696381.3248575</v>
+        <v>19852293.344365</v>
       </c>
       <c r="J3" t="n">
-        <v>4696070.6249155</v>
+        <v>19850960.7369275</v>
       </c>
     </row>
     <row r="4">
@@ -558,28 +558,28 @@
         <v>8759</v>
       </c>
       <c r="C4" t="n">
-        <v>41324434</v>
+        <v>41304657</v>
       </c>
       <c r="D4" t="n">
-        <v>27801942</v>
+        <v>27791802</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>13306055.14941759</v>
+        <v>13298856.93439061</v>
       </c>
       <c r="G4" t="n">
-        <v>173349.98</v>
+        <v>169979.43</v>
       </c>
       <c r="H4" t="n">
-        <v>-173349.98</v>
+        <v>-169979.43</v>
       </c>
       <c r="I4" t="n">
-        <v>86828387.579575</v>
+        <v>83664981.32948807</v>
       </c>
       <c r="J4" t="n">
-        <v>86831082.15900075</v>
+        <v>83681680.29514146</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,28 +490,28 @@
         <v>35036</v>
       </c>
       <c r="C2" t="n">
-        <v>525000</v>
+        <v>2400</v>
       </c>
       <c r="D2" t="n">
-        <v>525000</v>
+        <v>2400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-1.2725137e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>14482.08508911288</v>
+        <v>57.61360503129153</v>
       </c>
       <c r="G2" t="n">
-        <v>71653.867</v>
+        <v>1200</v>
       </c>
       <c r="H2" t="n">
-        <v>-71653.867</v>
+        <v>-1200</v>
       </c>
       <c r="I2" t="n">
-        <v>19239612.40794263</v>
+        <v>1351339.081612725</v>
       </c>
       <c r="J2" t="n">
-        <v>18948261.48692221</v>
+        <v>1351039.081575975</v>
       </c>
     </row>
     <row r="3">
@@ -524,28 +524,62 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>3588449.7</v>
+        <v>62140</v>
       </c>
       <c r="D3" t="n">
-        <v>3588449.7</v>
+        <v>62140</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3805432e-11</v>
+        <v>-1.5938014e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>313275.22446899</v>
+        <v>9338.856254838931</v>
       </c>
       <c r="G3" t="n">
-        <v>34830</v>
+        <v>6214</v>
       </c>
       <c r="H3" t="n">
-        <v>-34830</v>
+        <v>-6214</v>
       </c>
       <c r="I3" t="n">
-        <v>13557936.64661725</v>
+        <v>16444803.067718</v>
       </c>
       <c r="J3" t="n">
-        <v>13023257.45264375</v>
+        <v>16439393.726854</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wasserstoffkaverne_H2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8759</v>
+      </c>
+      <c r="C4" t="n">
+        <v>391077.08</v>
+      </c>
+      <c r="D4" t="n">
+        <v>349250.58</v>
+      </c>
+      <c r="E4" t="n">
+        <v>184843.33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>253807.214632949</v>
+      </c>
+      <c r="G4" t="n">
+        <v>547.50791</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-547.50791</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1965246.958859601</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1965520.7133866</v>
       </c>
     </row>
   </sheetData>

--- a/data/b_Optimierung/opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/opt_speicher_statistiken.xlsx
@@ -490,28 +490,28 @@
         <v>35036</v>
       </c>
       <c r="C2" t="n">
-        <v>45170.431</v>
+        <v>57012.294</v>
       </c>
       <c r="D2" t="n">
-        <v>45170.431</v>
+        <v>57012.294</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.3107066e-14</v>
+        <v>-2.7574241e-12</v>
       </c>
       <c r="F2" t="n">
-        <v>2465.805483493737</v>
+        <v>3744.286837901107</v>
       </c>
       <c r="G2" t="n">
-        <v>22585.215</v>
+        <v>28506.147</v>
       </c>
       <c r="H2" t="n">
-        <v>-22585.215</v>
+        <v>-28506.147</v>
       </c>
       <c r="I2" t="n">
-        <v>21497116.57352501</v>
+        <v>25472279.20241618</v>
       </c>
       <c r="J2" t="n">
-        <v>21491470.26829587</v>
+        <v>25465152.65868276</v>
       </c>
     </row>
     <row r="3">
@@ -524,28 +524,28 @@
         <v>8759</v>
       </c>
       <c r="C3" t="n">
-        <v>266521.3</v>
+        <v>304300</v>
       </c>
       <c r="D3" t="n">
-        <v>266521.3</v>
+        <v>304300</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.1580267e-11</v>
+        <v>-3.9864002e-11</v>
       </c>
       <c r="F3" t="n">
-        <v>59587.17277239982</v>
+        <v>66619.81165183696</v>
       </c>
       <c r="G3" t="n">
-        <v>26652.13</v>
+        <v>30430</v>
       </c>
       <c r="H3" t="n">
-        <v>-26652.13</v>
+        <v>-30430</v>
       </c>
       <c r="I3" t="n">
-        <v>19852293.344365</v>
+        <v>22941227.45833</v>
       </c>
       <c r="J3" t="n">
-        <v>19850960.7369275</v>
+        <v>22939705.95539525</v>
       </c>
     </row>
     <row r="4">
@@ -558,28 +558,28 @@
         <v>8759</v>
       </c>
       <c r="C4" t="n">
-        <v>41304657</v>
+        <v>49457381</v>
       </c>
       <c r="D4" t="n">
-        <v>27791802</v>
+        <v>32333475</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>13298856.93439061</v>
+        <v>17740048.28509464</v>
       </c>
       <c r="G4" t="n">
-        <v>169979.43</v>
+        <v>179069.22</v>
       </c>
       <c r="H4" t="n">
-        <v>-169979.43</v>
+        <v>-179069.22</v>
       </c>
       <c r="I4" t="n">
-        <v>83664981.32948807</v>
+        <v>91037246.01745999</v>
       </c>
       <c r="J4" t="n">
-        <v>83681680.29514146</v>
+        <v>91050068.83225887</v>
       </c>
     </row>
   </sheetData>
